--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486772_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486772_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7476</v>
+        <v>2.8772</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3831</v>
+        <v>3.4383</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.5611</v>
       </c>
       <c r="G2" t="n">
         <v>0.8829</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5572</v>
+        <v>-0.4275</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8554</v>
+        <v>-0.8002</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2982</v>
+        <v>0.3727</v>
       </c>
       <c r="V2" t="n">
         <v>0.4911</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5742</v>
+        <v>1.4921</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0435</v>
+        <v>2.5693</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4693</v>
+        <v>-1.0772</v>
       </c>
       <c r="G3" t="n">
-        <v>0.875</v>
+        <v>0.825</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9586</v>
+        <v>1.3586</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0837</v>
+        <v>-0.5336</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3443</v>
+        <v>2.7914</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3036</v>
+        <v>2.6693</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0407</v>
+        <v>0.1221</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4693</v>
+        <v>-1.9664</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.345</v>
+        <v>-1.3107</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1244</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2206</v>
+        <v>-0.5034</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4136</v>
+        <v>0.1721</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.193</v>
+        <v>-0.6756</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2856</v>
+        <v>1.1706</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.5993000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3114</v>
+        <v>1.2847</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5624</v>
+        <v>1.6298</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.251</v>
+        <v>-0.3451</v>
       </c>
       <c r="G4" t="n">
-        <v>0.825</v>
+        <v>0.875</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3586</v>
+        <v>0.9586</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5336</v>
+        <v>-0.0837</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7914</v>
+        <v>1.3443</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6693</v>
+        <v>1.3036</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1221</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9664</v>
+        <v>-0.4693</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3107</v>
+        <v>-0.345</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.1244</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.1931</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6842</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1652</v>
+        <v>-0.0001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8494</v>
+        <v>-0.0689</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1706</v>
+        <v>0.2856</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5993000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5545</v>
+        <v>0.9558</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9847</v>
+        <v>2.4605</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4302</v>
+        <v>-1.5047</v>
       </c>
       <c r="G5" t="n">
         <v>3.1157</v>
@@ -844,13 +844,13 @@
         <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5185</v>
+        <v>-0.1172</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7175</v>
+        <v>-0.2417</v>
       </c>
       <c r="U5" t="n">
-        <v>0.199</v>
+        <v>0.1245</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2703</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2291</v>
+        <v>-0.1216</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2867</v>
+        <v>-0.0799</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0576</v>
+        <v>-0.0417</v>
       </c>
       <c r="G6" t="n">
         <v>0.0576</v>
@@ -922,13 +922,13 @@
         <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.5653</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3311</v>
+        <v>-0.1242</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3418</v>
+        <v>-0.4411</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2771</v>
+        <v>-2.1505</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5089</v>
+        <v>0.3984</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7682</v>
+        <v>-2.5489</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4478</v>
+        <v>-0.4367</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.4689</v>
+        <v>-0.1586</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0211</v>
+        <v>-0.2781</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5602</v>
+        <v>2.0811</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.158</v>
+        <v>0.7383</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7182</v>
+        <v>1.3428</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.0081</v>
+        <v>-2.5178</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.3109</v>
+        <v>-0.8969</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3029</v>
+        <v>-1.6209</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3169</v>
+        <v>1.1585</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6840000000000001</v>
+        <v>-0.8276</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1384</v>
+        <v>-0.7174</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8224</v>
+        <v>-0.1102</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8995</v>
+        <v>-1.0793</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8995</v>
+        <v>-1.0793</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2995</v>
+        <v>-2.6164</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3984</v>
+        <v>-1.5502</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6978</v>
+        <v>-1.0662</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4367</v>
+        <v>-2.4478</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1586</v>
+        <v>-4.4689</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2781</v>
+        <v>2.0211</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0811</v>
+        <v>0.5602</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7383</v>
+        <v>-1.158</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3428</v>
+        <v>1.7182</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5178</v>
+        <v>-3.0081</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8969</v>
+        <v>-3.3109</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6209</v>
+        <v>0.3029</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1585</v>
+        <v>2.3169</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9765</v>
+        <v>0.3447</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7174</v>
+        <v>-0.1797</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2592</v>
+        <v>0.5244</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0793</v>
+        <v>-0.8995</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0793</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0829</v>
+        <v>-3.0277</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1444</v>
+        <v>-2.0892</v>
       </c>
       <c r="F9" t="n">
         <v>-0.9384</v>
@@ -1156,10 +1156,10 @@
         <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1104</v>
+        <v>-0.0552</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2484</v>
+        <v>-0.1932</v>
       </c>
       <c r="U9" t="n">
         <v>0.138</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9237</v>
+        <v>-3.8216</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4184</v>
+        <v>-0.3784</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5052</v>
+        <v>-3.4433</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2704</v>
+        <v>-2.7855</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0482</v>
+        <v>-0.179</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2222</v>
+        <v>-2.6065</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9795</v>
+        <v>1.2366</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2201</v>
+        <v>2.6494</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7594</v>
+        <v>-1.4128</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2909</v>
+        <v>-4.0221</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8282</v>
+        <v>-2.8284</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4627</v>
+        <v>-1.1937</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4468</v>
+        <v>-1.0067</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1107</v>
+        <v>-0.8693</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3361</v>
+        <v>-0.1375</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7511</v>
+        <v>-0.2225</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3282</v>
+        <v>1.1851</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4229</v>
+        <v>-1.4076</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9899</v>
+        <v>-3.9664</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6956</v>
+        <v>-2.4115</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2943</v>
+        <v>-1.5549</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7855</v>
+        <v>-4.2704</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.179</v>
+        <v>-2.0482</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6065</v>
+        <v>-2.2222</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2366</v>
+        <v>-1.9795</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6494</v>
+        <v>-1.2201</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4128</v>
+        <v>-0.7594</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.0221</v>
+        <v>-2.2909</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.8284</v>
+        <v>-0.8282</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1937</v>
+        <v>-1.4627</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.175</v>
+        <v>-0.4895</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1865</v>
+        <v>-0.1038</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0115</v>
+        <v>-0.3857</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2225</v>
+        <v>-0.7511</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1851</v>
+        <v>-0.3282</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4076</v>
+        <v>-0.4229</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.2335</v>
+        <v>-5.9259</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8421</v>
+        <v>-3.6835</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3915</v>
+        <v>-2.2425</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1669</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.4207</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4139</v>
+        <v>-0.2553</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3144</v>
+        <v>-0.1654</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4076</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.848</v>
+        <v>-15.0203</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5239999999999987</v>
+        <v>0.303599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.3239</v>
+        <v>-15.324</v>
       </c>
       <c r="G13" t="n">
         <v>-7.5513</v>
@@ -1459,7 +1459,7 @@
         <v>-5.2113</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9654999999999996</v>
+        <v>0.9655</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.5156</v>
@@ -1468,16 +1468,16 @@
         <v>14.481</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.9652</v>
+        <v>-4.1374</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.1405</v>
+        <v>-3.3128</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8248000000000001</v>
+        <v>-0.8248</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.2968</v>
+        <v>-4.296799999999999</v>
       </c>
       <c r="W13" t="n">
         <v>2.5706</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.7621</v>
+        <v>13.671</v>
       </c>
       <c r="E14" t="n">
-        <v>11.3136</v>
+        <v>11.6239</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4485</v>
+        <v>2.0471</v>
       </c>
       <c r="G14" t="n">
         <v>7.8514</v>
@@ -1546,13 +1546,13 @@
         <v>1.9308</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.309</v>
+        <v>0.5999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.2272</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2259</v>
+        <v>0.3727</v>
       </c>
       <c r="V14" t="n">
         <v>4.2543</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7219</v>
+        <v>3.6506</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2924</v>
+        <v>3.9479</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5705</v>
+        <v>-0.2973</v>
       </c>
       <c r="G15" t="n">
         <v>1.8274</v>
@@ -1624,13 +1624,13 @@
         <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6089</v>
+        <v>1.5376</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3716</v>
+        <v>1.0272</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2373</v>
+        <v>0.5104</v>
       </c>
       <c r="V15" t="n">
         <v>0.2856</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7504</v>
+        <v>3.4409</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8882</v>
+        <v>4.6631</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8622</v>
+        <v>-1.2221</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6261</v>
+        <v>2.4353</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9661</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.66</v>
+        <v>2.5183</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7241</v>
+        <v>4.8022</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8288</v>
+        <v>1.5039</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8952</v>
+        <v>3.2984</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.098</v>
+        <v>-2.367</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8628</v>
+        <v>-1.587</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2352</v>
+        <v>-0.78</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9654</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4179</v>
+        <v>0.8206</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7168</v>
+        <v>-0.0073</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.8279</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3282</v>
+        <v>0.5712</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6565</v>
+        <v>1.7989</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3282</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3226</v>
+        <v>2.5324</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7323</v>
+        <v>1.6814</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4097</v>
+        <v>0.8511</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4353</v>
+        <v>2.6261</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.08309999999999999</v>
+        <v>1.9661</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5183</v>
+        <v>0.66</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8022</v>
+        <v>4.7241</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5039</v>
+        <v>3.8288</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2984</v>
+        <v>0.8952</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.367</v>
+        <v>-2.098</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.587</v>
+        <v>-1.8628</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.78</v>
+        <v>-0.2352</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2977</v>
+        <v>1.1999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9381</v>
+        <v>0.5099</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6403</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5712</v>
+        <v>-0.3282</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7989</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6622</v>
+        <v>1.0788</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6279</v>
+        <v>1.4211</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9658</v>
+        <v>-0.3423</v>
       </c>
       <c r="G18" t="n">
         <v>0.3478</v>
@@ -1858,13 +1858,13 @@
         <v>2.3169</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0718</v>
+        <v>0.3448</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1934</v>
+        <v>-0.4003</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1216</v>
+        <v>0.7451</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.993</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3826</v>
+        <v>0.486</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2449</v>
+        <v>0.507</v>
       </c>
       <c r="G19" t="n">
         <v>0.1132</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3586</v>
+        <v>0.0069</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2759</v>
+        <v>-0.1725</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0827</v>
+        <v>0.1794</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3048</v>
+        <v>0.4784</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.501</v>
+        <v>-1.8804</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1961</v>
+        <v>2.3589</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7395</v>
@@ -2014,13 +2014,13 @@
         <v>1.9308</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5074</v>
+        <v>0.2759</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7725</v>
+        <v>-0.152</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2652</v>
+        <v>0.4279</v>
       </c>
       <c r="V20" t="n">
         <v>0.9421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.6691</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.787</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1772</v>
+        <v>-0.089</v>
       </c>
       <c r="G21" t="n">
         <v>-0.08409999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1158</v>
+        <v>0.1793</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5518</v>
+        <v>-0.345</v>
       </c>
       <c r="U21" t="n">
-        <v>0.436</v>
+        <v>0.5242</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5712</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0456</v>
+        <v>-2.7312</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6351</v>
+        <v>-1.7386</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4104</v>
+        <v>-0.9927</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1738</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8925</v>
+        <v>1.2069</v>
       </c>
       <c r="T22" t="n">
-        <v>0.248</v>
+        <v>0.1446</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6445</v>
+        <v>1.0623</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5712</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6841</v>
+        <v>-5.2179</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9901</v>
+        <v>-4.3003</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.9176</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6526</v>
@@ -2248,13 +2248,13 @@
         <v>0.1931</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7062</v>
+        <v>0.1724</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3032</v>
+        <v>-0.0071</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4029</v>
+        <v>0.1795</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>15.848</v>
+        <v>17.2269</v>
       </c>
       <c r="E24" t="n">
-        <v>15.3238</v>
+        <v>15.324</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5239999999999997</v>
+        <v>1.9031</v>
       </c>
       <c r="G24" t="n">
         <v>7.551199999999998</v>
@@ -2326,13 +2326,13 @@
         <v>13.5155</v>
       </c>
       <c r="S24" t="n">
-        <v>4.9652</v>
+        <v>6.3442</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8247999999999996</v>
+        <v>0.8247000000000003</v>
       </c>
       <c r="U24" t="n">
-        <v>4.1403</v>
+        <v>5.5194</v>
       </c>
       <c r="V24" t="n">
         <v>4.297</v>
